--- a/artfynd/A 46244-2024 artfynd.xlsx
+++ b/artfynd/A 46244-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150533</v>
+        <v>121150531</v>
       </c>
       <c r="B2" t="n">
-        <v>91963</v>
+        <v>92008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525996</v>
+        <v>525963</v>
       </c>
       <c r="R2" t="n">
-        <v>6870138</v>
+        <v>6870160</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150530</v>
+        <v>121150533</v>
       </c>
       <c r="B3" t="n">
-        <v>91979</v>
+        <v>91973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525955</v>
+        <v>525996</v>
       </c>
       <c r="R3" t="n">
-        <v>6870146</v>
+        <v>6870138</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150529</v>
+        <v>121150528</v>
       </c>
       <c r="B4" t="n">
-        <v>91963</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526081</v>
+        <v>526091</v>
       </c>
       <c r="R4" t="n">
-        <v>6870289</v>
+        <v>6870292</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150531</v>
+        <v>121150532</v>
       </c>
       <c r="B5" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525963</v>
+        <v>525990</v>
       </c>
       <c r="R5" t="n">
         <v>6870160</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150528</v>
+        <v>121150530</v>
       </c>
       <c r="B6" t="n">
-        <v>91979</v>
+        <v>91989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526091</v>
+        <v>525955</v>
       </c>
       <c r="R6" t="n">
-        <v>6870292</v>
+        <v>6870146</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150532</v>
+        <v>121150529</v>
       </c>
       <c r="B7" t="n">
-        <v>91998</v>
+        <v>91973</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525990</v>
+        <v>526081</v>
       </c>
       <c r="R7" t="n">
-        <v>6870160</v>
+        <v>6870289</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 46244-2024 artfynd.xlsx
+++ b/artfynd/A 46244-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150531</v>
+        <v>121150533</v>
       </c>
       <c r="B2" t="n">
-        <v>92008</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525963</v>
+        <v>525996</v>
       </c>
       <c r="R2" t="n">
-        <v>6870160</v>
+        <v>6870138</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150533</v>
+        <v>121150528</v>
       </c>
       <c r="B3" t="n">
-        <v>91973</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525996</v>
+        <v>526091</v>
       </c>
       <c r="R3" t="n">
-        <v>6870138</v>
+        <v>6870292</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150528</v>
+        <v>121150530</v>
       </c>
       <c r="B4" t="n">
         <v>91989</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526091</v>
+        <v>525955</v>
       </c>
       <c r="R4" t="n">
-        <v>6870292</v>
+        <v>6870146</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150532</v>
+        <v>121150529</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>91973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525990</v>
+        <v>526081</v>
       </c>
       <c r="R5" t="n">
-        <v>6870160</v>
+        <v>6870289</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150530</v>
+        <v>121150531</v>
       </c>
       <c r="B6" t="n">
-        <v>91989</v>
+        <v>92008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525955</v>
+        <v>525963</v>
       </c>
       <c r="R6" t="n">
-        <v>6870146</v>
+        <v>6870160</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150529</v>
+        <v>121150532</v>
       </c>
       <c r="B7" t="n">
-        <v>91973</v>
+        <v>92008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>526081</v>
+        <v>525990</v>
       </c>
       <c r="R7" t="n">
-        <v>6870289</v>
+        <v>6870160</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 46244-2024 artfynd.xlsx
+++ b/artfynd/A 46244-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150533</v>
+        <v>121150530</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>92001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525996</v>
+        <v>525955</v>
       </c>
       <c r="R2" t="n">
-        <v>6870138</v>
+        <v>6870146</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150528</v>
+        <v>121150531</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>92020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526091</v>
+        <v>525963</v>
       </c>
       <c r="R3" t="n">
-        <v>6870292</v>
+        <v>6870160</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150530</v>
+        <v>121150532</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
+        <v>92020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525955</v>
+        <v>525990</v>
       </c>
       <c r="R4" t="n">
-        <v>6870146</v>
+        <v>6870160</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150529</v>
+        <v>121150528</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>92001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526081</v>
+        <v>526091</v>
       </c>
       <c r="R5" t="n">
-        <v>6870289</v>
+        <v>6870292</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150531</v>
+        <v>121150533</v>
       </c>
       <c r="B6" t="n">
-        <v>92008</v>
+        <v>91985</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525963</v>
+        <v>525996</v>
       </c>
       <c r="R6" t="n">
-        <v>6870160</v>
+        <v>6870138</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150532</v>
+        <v>121150529</v>
       </c>
       <c r="B7" t="n">
-        <v>92008</v>
+        <v>91985</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525990</v>
+        <v>526081</v>
       </c>
       <c r="R7" t="n">
-        <v>6870160</v>
+        <v>6870289</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 46244-2024 artfynd.xlsx
+++ b/artfynd/A 46244-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150530</v>
+        <v>121150533</v>
       </c>
       <c r="B2" t="n">
-        <v>92001</v>
+        <v>91986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525955</v>
+        <v>525996</v>
       </c>
       <c r="R2" t="n">
-        <v>6870146</v>
+        <v>6870138</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150531</v>
+        <v>121150529</v>
       </c>
       <c r="B3" t="n">
-        <v>92020</v>
+        <v>91986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525963</v>
+        <v>526081</v>
       </c>
       <c r="R3" t="n">
-        <v>6870160</v>
+        <v>6870289</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150532</v>
+        <v>121150531</v>
       </c>
       <c r="B4" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525990</v>
+        <v>525963</v>
       </c>
       <c r="R4" t="n">
         <v>6870160</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150528</v>
+        <v>121150530</v>
       </c>
       <c r="B5" t="n">
-        <v>92001</v>
+        <v>92002</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526091</v>
+        <v>525955</v>
       </c>
       <c r="R5" t="n">
-        <v>6870292</v>
+        <v>6870146</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150533</v>
+        <v>121150528</v>
       </c>
       <c r="B6" t="n">
-        <v>91985</v>
+        <v>92002</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525996</v>
+        <v>526091</v>
       </c>
       <c r="R6" t="n">
-        <v>6870138</v>
+        <v>6870292</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150529</v>
+        <v>121150532</v>
       </c>
       <c r="B7" t="n">
-        <v>91985</v>
+        <v>92021</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>526081</v>
+        <v>525990</v>
       </c>
       <c r="R7" t="n">
-        <v>6870289</v>
+        <v>6870160</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 46244-2024 artfynd.xlsx
+++ b/artfynd/A 46244-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150533</v>
+        <v>121150528</v>
       </c>
       <c r="B2" t="n">
-        <v>91986</v>
+        <v>92005</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525996</v>
+        <v>526091</v>
       </c>
       <c r="R2" t="n">
-        <v>6870138</v>
+        <v>6870292</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150529</v>
+        <v>121150530</v>
       </c>
       <c r="B3" t="n">
-        <v>91986</v>
+        <v>92005</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526081</v>
+        <v>525955</v>
       </c>
       <c r="R3" t="n">
-        <v>6870289</v>
+        <v>6870146</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150531</v>
+        <v>121150533</v>
       </c>
       <c r="B4" t="n">
-        <v>92021</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525963</v>
+        <v>525996</v>
       </c>
       <c r="R4" t="n">
-        <v>6870160</v>
+        <v>6870138</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150530</v>
+        <v>121150531</v>
       </c>
       <c r="B5" t="n">
-        <v>92002</v>
+        <v>92024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525955</v>
+        <v>525963</v>
       </c>
       <c r="R5" t="n">
-        <v>6870146</v>
+        <v>6870160</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150528</v>
+        <v>121150532</v>
       </c>
       <c r="B6" t="n">
-        <v>92002</v>
+        <v>92024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526091</v>
+        <v>525990</v>
       </c>
       <c r="R6" t="n">
-        <v>6870292</v>
+        <v>6870160</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150532</v>
+        <v>121150529</v>
       </c>
       <c r="B7" t="n">
-        <v>92021</v>
+        <v>91989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525990</v>
+        <v>526081</v>
       </c>
       <c r="R7" t="n">
-        <v>6870160</v>
+        <v>6870289</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 46244-2024 artfynd.xlsx
+++ b/artfynd/A 46244-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150528</v>
+        <v>121150529</v>
       </c>
       <c r="B2" t="n">
-        <v>92005</v>
+        <v>91989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526091</v>
+        <v>526081</v>
       </c>
       <c r="R2" t="n">
-        <v>6870292</v>
+        <v>6870289</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150533</v>
+        <v>121150532</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
+        <v>92024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525996</v>
+        <v>525990</v>
       </c>
       <c r="R4" t="n">
-        <v>6870138</v>
+        <v>6870160</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150532</v>
+        <v>121150533</v>
       </c>
       <c r="B6" t="n">
-        <v>92024</v>
+        <v>91989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525990</v>
+        <v>525996</v>
       </c>
       <c r="R6" t="n">
-        <v>6870160</v>
+        <v>6870138</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150529</v>
+        <v>121150528</v>
       </c>
       <c r="B7" t="n">
-        <v>91989</v>
+        <v>92005</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>526081</v>
+        <v>526091</v>
       </c>
       <c r="R7" t="n">
-        <v>6870289</v>
+        <v>6870292</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 46244-2024 artfynd.xlsx
+++ b/artfynd/A 46244-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150529</v>
+        <v>121150528</v>
       </c>
       <c r="B2" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526081</v>
+        <v>526091</v>
       </c>
       <c r="R2" t="n">
-        <v>6870289</v>
+        <v>6870292</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,16 +784,11 @@
         <v>121150530</v>
       </c>
       <c r="B3" t="n">
-        <v>92005</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150532</v>
+        <v>121150529</v>
       </c>
       <c r="B4" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525990</v>
+        <v>526081</v>
       </c>
       <c r="R4" t="n">
-        <v>6870160</v>
+        <v>6870289</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150531</v>
+        <v>121150533</v>
       </c>
       <c r="B5" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525963</v>
+        <v>525996</v>
       </c>
       <c r="R5" t="n">
-        <v>6870160</v>
+        <v>6870138</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150533</v>
+        <v>121150531</v>
       </c>
       <c r="B6" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525996</v>
+        <v>525963</v>
       </c>
       <c r="R6" t="n">
-        <v>6870138</v>
+        <v>6870160</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121150528</v>
+        <v>121150532</v>
       </c>
       <c r="B7" t="n">
-        <v>92005</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>526091</v>
+        <v>525990</v>
       </c>
       <c r="R7" t="n">
-        <v>6870292</v>
+        <v>6870160</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 46244-2024 artfynd.xlsx
+++ b/artfynd/A 46244-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150528</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150530</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150529</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150533</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150531</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150532</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>